--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>包含理學檢查中各系統部位代碼之值集。</t>
+    <t>【依據：勞工健康保護規則附表】包含理學檢查中各系統部位代碼之值集。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-PhysicalExamSystems.xlsx
+++ b/ValueSet-VS-PhysicalExamSystems.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
